--- a/tests/TC-12/results/teacher_timetables_even.xlsx
+++ b/tests/TC-12/results/teacher_timetables_even.xlsx
@@ -646,35 +646,35 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>CS999 LEC
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>CS999 LEC
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>CS999 LEC
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>CS999 LEC
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
+      <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr"/>
@@ -706,28 +706,28 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>CS999 TUT
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>CS999 LEC
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>CS999 TUT
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>CS999 LEC
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>CS999 TUT
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>CS999 LEC
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
@@ -749,20 +749,8 @@
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>CS999 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>CS999 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
       <c r="O6" s="4" t="inlineStr"/>
       <c r="P6" s="4" t="inlineStr"/>
       <c r="Q6" s="4" t="inlineStr"/>
@@ -795,7 +783,13 @@
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr"/>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>CS999 TUT
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
   </sheetData>

--- a/tests/TC-12/results/teacher_timetables_even.xlsx
+++ b/tests/TC-12/results/teacher_timetables_even.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-        <bgColor rgb="00BBDEFB"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
   </fills>
@@ -646,34 +646,10 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>CS999 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>CS999 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>CS999 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>CS999 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr"/>
@@ -707,29 +683,17 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>CS999 LEC
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>CS999 TUT
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>CS999 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>CS999 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
@@ -750,9 +714,27 @@
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>CS999 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>CS999 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>CS999 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="Q6" s="4" t="inlineStr"/>
       <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr"/>
@@ -780,16 +762,28 @@
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="6" t="inlineStr">
-        <is>
-          <t>CS999 TUT
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>CS999 LEC
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>CS999 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>CS999 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
